--- a/AAII_Financials/Quarterly/NAVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NAVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
   <si>
     <t>NAVI</t>
   </si>
@@ -656,292 +656,299 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E8" s="3">
         <v>125000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>93000</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3">
         <v>119000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>126000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>206000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>135000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>233000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>275000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>175000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>350000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>296000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>336000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>295000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>320000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>409000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>434000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>437000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>469000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>464000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>502000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>464000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>461000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>402000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>383000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>418000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>435000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>416000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>404000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>425000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>412000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>397000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>438000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>474000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>512000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>462000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>440000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>480000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>509000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -984,208 +991,214 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>-17000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>-24000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>-17000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>-18000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>-19000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>-47000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>-50000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>-53000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>-51000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>-54000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>-52000</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>-58000</v>
       </c>
       <c r="AC9" s="3">
         <v>-58000</v>
       </c>
       <c r="AD9" s="3">
-        <v>-60000</v>
+        <v>-58000</v>
       </c>
       <c r="AE9" s="3">
         <v>-60000</v>
       </c>
       <c r="AF9" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="AG9" s="3">
         <v>-62000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>-64000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>-70000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>-71000</v>
-      </c>
-      <c r="AJ9" s="3">
-        <v>-69000</v>
       </c>
       <c r="AK9" s="3">
         <v>-69000</v>
       </c>
       <c r="AL9" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="AM9" s="3">
         <v>-75000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>-70000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>-76000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>-74000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>-76000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E10" s="3">
         <v>125000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>93000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-7000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>119000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>126000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>206000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>135000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>233000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>275000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>175000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>350000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>296000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>336000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>312000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>344000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>426000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>452000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>456000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>516000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>514000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>555000</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>515000</v>
       </c>
       <c r="Z10" s="3">
         <v>515000</v>
       </c>
       <c r="AA10" s="3">
+        <v>515000</v>
+      </c>
+      <c r="AB10" s="3">
         <v>454000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>441000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>476000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>495000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>476000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>466000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>489000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>482000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>468000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>507000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>543000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>587000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>532000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>516000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>554000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>585000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1228,8 +1241,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1350,8 +1364,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1472,115 +1489,118 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>11000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>3000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>32000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-63000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>16000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>10000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>15000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>13000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>31000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>67000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>24000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>19000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>11000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>8000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>18000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>47000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>94000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>9000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>8000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>12000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>8000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>11000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>24000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>16000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>35000</v>
-      </c>
-      <c r="AL14" s="3">
-        <v>6000</v>
       </c>
       <c r="AM14" s="3">
         <v>6000</v>
@@ -1589,21 +1609,24 @@
         <v>6000</v>
       </c>
       <c r="AO14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AP14" s="3">
         <v>14000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>4000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1000</v>
       </c>
       <c r="F15" s="3">
         <v>1000</v>
@@ -1618,19 +1641,19 @@
         <v>1000</v>
       </c>
       <c r="J15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K15" s="3">
         <v>2000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>3000</v>
       </c>
       <c r="L15" s="3">
         <v>3000</v>
       </c>
       <c r="M15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N15" s="3">
         <v>2000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>3000</v>
       </c>
       <c r="O15" s="3">
         <v>3000</v>
@@ -1638,11 +1661,11 @@
       <c r="P15" s="3">
         <v>3000</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1716,8 +1739,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1757,252 +1783,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E17" s="3">
         <v>93000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>89000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>106000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>101000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>128000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>148000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>186000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>169000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>186000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>201000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>236000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>185000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>188000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>181000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>183000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>165000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>102000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>446000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>249000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>224000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>230000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>202000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>232000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>514000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>199000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>250000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>222000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>240000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>318000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>265000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>284000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>276000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>292000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>243000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>290000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>299000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>238000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>132000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E18" s="3">
         <v>32000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-113000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>58000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-51000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>64000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>89000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-26000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>114000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>111000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>148000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>114000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>137000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>244000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>332000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>220000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>240000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>484000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>234000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>259000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>170000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-131000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>219000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>185000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>194000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>164000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>107000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>147000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>113000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>162000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>182000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>269000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>172000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>141000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>242000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>377000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2045,8 +2078,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2089,8 +2123,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -2167,53 +2201,56 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E21" s="3">
         <v>36000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-112000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>19000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>59000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-49000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>67000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>92000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-24000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>117000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>114000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>151000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2280,17 +2317,20 @@
       <c r="AM21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AN21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO21" s="3">
         <v>141000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>242000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>377000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2333,8 +2373,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2411,252 +2451,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E23" s="3">
         <v>32000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-117000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>26000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>48000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>88000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-36000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>110000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>96000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>144000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>114000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>137000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>244000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>332000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>220000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>240000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>484000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>234000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>259000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>170000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-131000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>219000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>185000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>194000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>164000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>107000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>147000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>113000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>162000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>182000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>269000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>172000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>141000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>242000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>377000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E24" s="3">
         <v>15000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-31000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-8000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>31000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>30000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>33000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>32000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>64000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>77000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>47000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>55000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>114000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>49000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>52000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>45000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>47000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>40000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>41000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>36000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>35000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>54000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>46000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>59000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>474000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>93000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>60000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>53000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>96000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>147000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2777,252 +2826,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E26" s="3">
         <v>17000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-86000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>24000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>36000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>73000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>79000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>66000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>111000</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>105000</v>
       </c>
       <c r="R26" s="3">
         <v>105000</v>
       </c>
       <c r="S26" s="3">
+        <v>105000</v>
+      </c>
+      <c r="T26" s="3">
         <v>180000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>255000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>173000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>185000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>370000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>185000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>207000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>125000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-106000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>172000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>145000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>153000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>128000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>72000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>93000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>67000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>103000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-292000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>176000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>112000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>88000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>146000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>230000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E27" s="3">
         <v>17000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-86000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>24000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>36000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>73000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-28000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>79000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>66000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>111000</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>105000</v>
       </c>
       <c r="R27" s="3">
         <v>105000</v>
       </c>
       <c r="S27" s="3">
+        <v>105000</v>
+      </c>
+      <c r="T27" s="3">
         <v>180000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>255000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-11000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>173000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>185000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>370000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>185000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>207000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>125000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-106000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>172000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>145000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>153000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>128000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>72000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>93000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>67000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>103000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-292000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>176000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>112000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>88000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>146000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>230000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3143,8 +3201,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3220,8 +3281,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -3235,38 +3296,41 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>21000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>16000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>23000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>208000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3387,8 +3451,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3509,8 +3576,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3553,8 +3623,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3631,130 +3701,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E33" s="3">
         <v>17000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-86000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>24000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>36000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>73000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>79000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>66000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>111000</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>105000</v>
       </c>
       <c r="R33" s="3">
         <v>105000</v>
       </c>
       <c r="S33" s="3">
+        <v>105000</v>
+      </c>
+      <c r="T33" s="3">
         <v>180000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>255000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-11000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>173000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>185000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>370000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>185000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>207000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>125000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-106000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>172000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>145000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>153000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>128000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>72000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>114000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>83000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>126000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-84000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>176000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>112000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>88000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>146000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>230000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3875,257 +3951,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E35" s="3">
         <v>17000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-86000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>24000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>36000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>73000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>79000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>66000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>111000</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>105000</v>
       </c>
       <c r="R35" s="3">
         <v>105000</v>
       </c>
       <c r="S35" s="3">
+        <v>105000</v>
+      </c>
+      <c r="T35" s="3">
         <v>180000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>255000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-11000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>173000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>185000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>370000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>185000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>207000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>125000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-106000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>172000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>145000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>153000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>128000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>72000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>114000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>83000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>126000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-84000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>176000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>112000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>88000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>146000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>230000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4168,8 +4253,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4212,175 +4298,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>770000</v>
+      </c>
+      <c r="E41" s="3">
         <v>621000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>637000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>571000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>712000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>642000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>722000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1143000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1088000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>823000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>839000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>977000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1317000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>570000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1535000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1364000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>976000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>708000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>905000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1050000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1453000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1497000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1183000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1775000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1632000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1084000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1233000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1583000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1746000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1206000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1286000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2143000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1622000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2398000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1518000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1248000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1153000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1364000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1253000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1823000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E42" s="3">
         <v>36000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>42000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>48000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>47000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>37000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>25000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>60000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>32000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>37000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>55000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>17000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>53000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>73000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4456,130 +4546,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>44039000</v>
+      </c>
+      <c r="E43" s="3">
         <v>44651000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>45412000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>46230000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>46928000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>47738000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>48470000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>49440000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>51199000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>54667000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>57131000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>59198000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>60861000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>62655000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2114000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2024000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1974000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1943000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2040000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2029000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2018000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1990000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2051000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2059000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2096000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1969000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2071000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1985000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2093000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2032000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2094000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2132000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2238000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2078000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2345000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1939000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1930000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1704000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1758000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1652000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4622,8 +4718,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4700,8 +4796,11 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4744,8 +4843,8 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4822,53 +4921,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>46256000</v>
+      </c>
+      <c r="E46" s="3">
         <v>46870000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>47598000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>48190000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>49091000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>49854000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>50628000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>52322000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>55275000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>57689000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>60025000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>62067000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>64243000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>65557000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4944,130 +5046,136 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E47" s="3">
         <v>96000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>126000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>107000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>96000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>101000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>113000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>111000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>94000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>92000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>100000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>98000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>97000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>102000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>62549000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>66363000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>69279000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>71566000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>73448000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>75009000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>75946000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>77243000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>80102000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>81620000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>83192000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>85681000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>87289000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>88468000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>90021000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>92560000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>95064000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>97556000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>100093000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>103054000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>105932000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>108311000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>111582000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>108989000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>112293000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>115487000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -5075,85 +5183,85 @@
         <v>21000</v>
       </c>
       <c r="E48" s="3">
+        <v>21000</v>
+      </c>
+      <c r="F48" s="3">
         <v>23000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>27000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>52000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>54000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>59000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>61000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>62000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>67000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>68000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>69000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>74000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>77000</v>
-      </c>
-      <c r="S48" s="3">
-        <v>91000</v>
       </c>
       <c r="T48" s="3">
         <v>91000</v>
       </c>
       <c r="U48" s="3">
+        <v>91000</v>
+      </c>
+      <c r="V48" s="3">
         <v>95000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>114000</v>
-      </c>
-      <c r="W48" s="3">
-        <v>113000</v>
       </c>
       <c r="X48" s="3">
         <v>113000</v>
       </c>
       <c r="Y48" s="3">
+        <v>113000</v>
+      </c>
+      <c r="Z48" s="3">
         <v>116000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>127000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>129000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>132000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>135000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>134000</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>136000</v>
       </c>
       <c r="AF48" s="3">
         <v>136000</v>
@@ -5162,34 +5270,37 @@
         <v>136000</v>
       </c>
       <c r="AH48" s="3">
+        <v>136000</v>
+      </c>
+      <c r="AI48" s="3">
         <v>107000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>104000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>150000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>108000</v>
-      </c>
-      <c r="AL48" s="3">
-        <v>152000</v>
       </c>
       <c r="AM48" s="3">
         <v>152000</v>
       </c>
       <c r="AN48" s="3">
+        <v>152000</v>
+      </c>
+      <c r="AO48" s="3">
         <v>157000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>160000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>156000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5197,121 +5308,124 @@
         <v>430000</v>
       </c>
       <c r="E49" s="3">
+        <v>430000</v>
+      </c>
+      <c r="F49" s="3">
         <v>434000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>435000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>436000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>437000</v>
       </c>
       <c r="I49" s="3">
         <v>437000</v>
       </c>
       <c r="J49" s="3">
+        <v>437000</v>
+      </c>
+      <c r="K49" s="3">
         <v>438000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>690000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>692000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>695000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>697000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>700000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>703000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>705000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>708000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>718000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>722000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>725000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>721000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>726000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>731000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>735000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>741000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>746000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>752000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>757000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>763000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>769000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>780000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>786000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>792000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>798000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>802000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>810000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>727000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>658000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>664000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>670000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>683000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5432,8 +5546,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5554,130 +5671,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>526000</v>
+      </c>
+      <c r="E52" s="3">
         <v>587000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>500000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>547000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>571000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>524000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>559000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>515000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>504000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>495000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>493000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>485000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>490000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>482000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3724000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2998000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2912000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2962000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3135000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2721000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2776000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3072000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2823000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2905000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2820000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3141000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3007000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3134000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3140000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3470000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4446000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3243000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>3530000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>3880000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>3402000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>3873000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>4084000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>4211000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>4088000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>4103000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5798,130 +5921,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>47297000</v>
+      </c>
+      <c r="E54" s="3">
         <v>48004000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>48681000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>49306000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>50222000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>50950000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>51789000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>53440000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>56622000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>59029000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>61375000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>63414000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>65598000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>66913000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>70795000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>73625000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>76065000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>78158000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>80605000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>81939000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>83348000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>84957000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>87412000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>89664000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>91045000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>93245000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>94903000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>96553000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>98320000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>100579000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>104176000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>106493000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>108949000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>113209000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>114991000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>117085000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>120354000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>117890000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>121136000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>125312000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5964,8 +6093,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6008,8 +6138,9 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -6052,8 +6183,8 @@
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -6130,130 +6261,136 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4305000</v>
+      </c>
+      <c r="E58" s="3">
         <v>5961000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5152000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4999000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4831000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5045000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5378000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5469000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5549000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4651000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4416000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4913000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5074000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5980000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5870000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5677000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4609000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3802000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2490000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2781000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4068000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5684000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6613000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7078000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7310000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>8452000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>8483000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7004000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>6785000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7505000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>5422000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>5007000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>4752000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>5131000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>4771000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3281000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3918000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>2160000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>2334000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>2637000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6296,8 +6433,8 @@
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
@@ -6374,53 +6511,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4305000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5961000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5152000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4999000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4831000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5045000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5378000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5469000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5549000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4651000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4416000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4913000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5074000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5980000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6496,175 +6636,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>40123000</v>
+      </c>
+      <c r="E61" s="3">
         <v>39240000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>40633000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>41414000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>42345000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>42872000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>43184000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>44695000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>47545000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50848000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>53402000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>54907000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>56936000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>57388000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>61026000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>63998000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>67738000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>70825000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>74488000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>75629000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>75814000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>75674000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>77332000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>79137000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>80260000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>81297000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>81715000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>84769000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>86776000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>88140000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>93519000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>96089000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>98690000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>102797000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>105012000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>108557000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>110778000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>109586000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>112368000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>116540000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>471000</v>
+      </c>
+      <c r="E62" s="3">
         <v>424000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>497000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>454000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>482000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>444000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>586000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>582000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>780000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>764000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>797000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>696000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>658000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>587000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6740,8 +6886,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6862,8 +7011,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6984,8 +7136,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7106,130 +7261,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>44899000</v>
+      </c>
+      <c r="E66" s="3">
         <v>45625000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>46282000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>46867000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>47658000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48361000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>49148000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>50746000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53874000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>56263000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>58615000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>60516000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>62668000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>63955000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>67818000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>70652000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>73138000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>75334000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>78008000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>79216000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>80647000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>82234000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>84979000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>87410000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>88930000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>91210000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>91567000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>93313000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>95019000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>97149000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>100657000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>102769000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>105235000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>109572000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>111537000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>113559000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>116814000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>114242000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>117437000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>121602000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7272,8 +7433,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7394,8 +7556,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7516,8 +7681,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7638,8 +7806,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7760,130 +7931,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4552000</v>
+        <v>4562000</v>
       </c>
       <c r="E72" s="3">
         <v>4552000</v>
       </c>
       <c r="F72" s="3">
+        <v>4552000</v>
+      </c>
+      <c r="G72" s="3">
         <v>4573000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4674000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4677000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4697000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4690000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4710000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4691000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4638000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4685000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4625000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4579000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4490000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4406000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4323000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4167000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3939000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3975000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3828000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3670000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3331000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3175000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2999000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2905000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3664000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3527000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3418000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3303000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>3218000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>3186000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>3114000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>3073000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3004000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3130000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2997000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>2930000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>2890000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>2858000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8004,8 +8181,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8126,8 +8306,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8248,130 +8431,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2398000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2379000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2399000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2439000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2564000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2589000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2641000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2694000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2748000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2766000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2760000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2898000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2930000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2958000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2977000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2973000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2927000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2824000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2597000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2723000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2701000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2723000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2433000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2254000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2115000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2035000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3336000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3240000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3301000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3430000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3519000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3724000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3714000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3637000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3454000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3526000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3540000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3648000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3699000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3710000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8492,257 +8681,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E81" s="3">
         <v>17000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-86000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>24000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>36000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>73000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>79000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>66000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>111000</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>105000</v>
       </c>
       <c r="R81" s="3">
         <v>105000</v>
       </c>
       <c r="S81" s="3">
+        <v>105000</v>
+      </c>
+      <c r="T81" s="3">
         <v>180000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>255000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-11000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>173000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>185000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>370000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>185000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>207000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>125000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-106000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>172000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>145000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>153000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>128000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>72000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>114000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>83000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>126000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-84000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>176000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>112000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>88000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>146000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>230000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8785,16 +8983,17 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E83" s="3">
-        <v>-137000</v>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>8</v>
@@ -8817,20 +9016,20 @@
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>-3000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8907,8 +9106,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9029,8 +9231,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9151,8 +9356,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9273,8 +9481,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9395,8 +9606,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9517,130 +9731,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-47000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>174000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>70000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>126000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>71000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>279000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>182000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>310000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>122000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>99000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>145000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>207000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>68000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>139000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-109000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>168000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>201000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>154000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>179000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>171000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>221000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>142000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>453000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>188000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>309000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>334000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>188000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>485000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>173000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>198000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>284000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>244000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>284000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>280000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>350000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>243000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>343000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9683,8 +9903,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9727,8 +9948,8 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9805,8 +10026,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9927,8 +10151,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10049,130 +10276,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>639000</v>
+      </c>
+      <c r="E94" s="3">
         <v>691000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>747000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>559000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>745000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>661000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>907000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1961000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3268000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2330000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2024000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1659000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1826000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1848000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>3773000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2856000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2205000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1751000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1560000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>894000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1334000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>2885000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1530000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1526000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>2407000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>985000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1079000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1525000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>2473000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>2408000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>2161000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>2443000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>3035000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>2721000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>2424000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>3194000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1133000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>3011000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>2913000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>3111000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10215,8 +10448,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10227,7 +10461,7 @@
         <v>15000</v>
       </c>
       <c r="F96" s="3">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="G96" s="3">
         <v>16000</v>
@@ -10236,19 +10470,19 @@
         <v>16000</v>
       </c>
       <c r="I96" s="3">
+        <v>16000</v>
+      </c>
+      <c r="J96" s="3">
         <v>17000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>18000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>17000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>18000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>19000</v>
       </c>
       <c r="N96" s="3">
         <v>19000</v>
@@ -10257,37 +10491,37 @@
         <v>19000</v>
       </c>
       <c r="P96" s="3">
+        <v>19000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>21000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-22000</v>
       </c>
       <c r="R96" s="3">
         <v>-22000</v>
       </c>
       <c r="S96" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-23000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-24000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-25000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-26000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-27000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-30000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-31000</v>
       </c>
       <c r="AA96" s="3">
         <v>-31000</v>
@@ -10296,49 +10530,52 @@
         <v>-31000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-35000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-36000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-37000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-39000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-40000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-41000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-43000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-42000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-43000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-42000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-45000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-46000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-47000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-49000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10459,8 +10696,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10581,8 +10821,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10703,130 +10946,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-774000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-617000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-689000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-834000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-849000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-780000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1605000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3164000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2489000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2357000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2342000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2248000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1435000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4022000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3085000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2448000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2122000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2006000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1461000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1546000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1828000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2499000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2378000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1522000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2328000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1451000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1746000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2000000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2601000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3638000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2632000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2376000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4022000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1854000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2411000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-3330000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>649000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-3250000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-3726000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-3008000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10869,8 +11118,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10947,126 +11196,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E102" s="3">
         <v>27000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>232000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-205000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>22000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-48000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-690000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1213000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1058000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>155000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-467000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>490000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2029000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>895000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>476000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>222000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-364000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>267000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-451000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-340000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>565000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-677000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>225000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>221000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-13000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-479000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-166000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>206000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1042000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>14000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>240000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-789000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1151000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>270000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>91000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-207000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>111000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-570000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>446000</v>
       </c>
     </row>
